--- a/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/8.2服务配置.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/8.2服务配置.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,25 +444,10 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>parentRowId</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>saleCode</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>internalSeq</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>预案版本号</t>
         </is>
@@ -492,19 +477,12 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -530,19 +508,12 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -568,19 +539,12 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -606,19 +570,12 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -644,19 +601,12 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -684,25 +634,10 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>d63ca370-ce45-4870-bbd1-0616c73704c2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>8814283352</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -730,25 +665,10 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>d63ca370-ce45-4870-bbd1-0616c73704c2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>8814283352</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -776,25 +696,10 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>d63ca370-ce45-4870-bbd1-0616c73704c2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>8814283352</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -822,25 +727,10 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>d63ca370-ce45-4870-bbd1-0616c73704c2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>8814283352</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -868,25 +758,10 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>d63ca370-ce45-4870-bbd1-0616c73704c2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>8814283352</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -914,25 +789,10 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>d63ca370-ce45-4870-bbd1-0616c73704c2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8814283352</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -960,25 +820,10 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>d63ca370-ce45-4870-bbd1-0616c73704c2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>8814283352</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1006,25 +851,10 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21b25b7d-57f1-4672-acb7-d9872565dbba</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>8814341929</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0002</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1052,25 +882,10 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21b25b7d-57f1-4672-acb7-d9872565dbba</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>8814341929</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0002</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1098,25 +913,10 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21b25b7d-57f1-4672-acb7-d9872565dbba</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>8814341929</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0002</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1144,25 +944,10 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21b25b7d-57f1-4672-acb7-d9872565dbba</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>8814341929</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0002</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1190,25 +975,10 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>cee771b9-ee1b-44b5-bf04-c3e805b35a05</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>8828122025</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0009</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1236,25 +1006,10 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>cee771b9-ee1b-44b5-bf04-c3e805b35a05</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>8828122024</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0010</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1282,25 +1037,10 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>80482ba7-7efe-4307-89e5-643ab09db543</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>88134UGF</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0011</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1328,25 +1068,10 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>79a3c3c6-12a5-4879-a5cb-68cc5a70535b</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>8803015789</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0012</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1374,25 +1099,10 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>79a3c3c6-12a5-4879-a5cb-68cc5a70535b</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>8803015790</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0013</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1420,25 +1130,10 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>79a3c3c6-12a5-4879-a5cb-68cc5a70535b</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>88065KVB</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0014</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1466,25 +1161,10 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>79a3c3c6-12a5-4879-a5cb-68cc5a70535b</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>88065KVH</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0015</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
